--- a/backend/data/financials_by_company/1620.HK.xlsx
+++ b/backend/data/financials_by_company/1620.HK.xlsx
@@ -4135,7 +4135,7 @@
         <v>-353000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
         <v>1.954</v>
@@ -4335,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
